--- a/snowy-plugin/snowy-plugin-sys/snowy-plugin-sys-func/src/main/resources/GZTemplateTwo.xlsx
+++ b/snowy-plugin/snowy-plugin-sys/snowy-plugin-sys-func/src/main/resources/GZTemplateTwo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="495" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="495"/>
   </bookViews>
   <sheets>
     <sheet name="工资" sheetId="40" r:id="rId1"/>
@@ -694,7 +694,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -733,11 +733,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color auto="1"/>
       </left>
-      <right/>
-      <top style="medium">
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="thin">
@@ -746,11 +748,13 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="thin">
@@ -768,7 +772,7 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -783,18 +787,7 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -803,8 +796,10 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
-      <top style="thin">
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
         <color auto="1"/>
       </top>
       <bottom style="thin">
@@ -819,7 +814,7 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="thin">
@@ -837,7 +832,7 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -971,7 +966,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -983,34 +978,34 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1117,7 +1112,7 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1150,65 +1145,53 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="59">
@@ -1621,8 +1604,8 @@
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
       <c r="I1" s="7"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
       <c r="L1" s="6"/>
       <c r="M1" s="7"/>
       <c r="N1" s="6"/>
@@ -1657,211 +1640,211 @@
       <c r="F2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="13"/>
-      <c r="H2" s="14" t="s">
+      <c r="G2" s="11"/>
+      <c r="H2" s="12" t="s">
         <v>5</v>
       </c>
       <c r="I2" s="11"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="22" t="s">
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="23" t="s">
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="23"/>
-      <c r="U2" s="27" t="s">
+      <c r="T2" s="10"/>
+      <c r="U2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="V2" s="27" t="s">
+      <c r="V2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="W2" s="27"/>
+      <c r="W2" s="23"/>
       <c r="X2" s="10" t="s">
         <v>10</v>
       </c>
       <c r="Y2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z2" s="22" t="s">
+      <c r="Z2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="AA2" s="26"/>
-      <c r="AB2" s="27" t="s">
+      <c r="AA2" s="10"/>
+      <c r="AB2" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="AC2" s="30" t="s">
+      <c r="AC2" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="39.95" customHeight="1" spans="1:29">
-      <c r="A3" s="15"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="17" t="s">
+      <c r="A3" s="13"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="24" t="s">
+      <c r="J3" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="25" t="s">
+      <c r="K3" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="25" t="s">
+      <c r="L3" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="17" t="s">
+      <c r="M3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="25" t="s">
+      <c r="N3" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="17" t="s">
+      <c r="O3" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="P3" s="17" t="s">
+      <c r="P3" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="Q3" s="17" t="s">
+      <c r="Q3" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="R3" s="17" t="s">
+      <c r="R3" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="17" t="s">
+      <c r="S3" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="T3" s="28" t="s">
+      <c r="T3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="16"/>
-      <c r="V3" s="25" t="s">
+      <c r="U3" s="14"/>
+      <c r="V3" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="W3" s="17" t="s">
+      <c r="W3" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="X3" s="29"/>
-      <c r="Y3" s="29"/>
-      <c r="Z3" s="17" t="s">
+      <c r="X3" s="24"/>
+      <c r="Y3" s="24"/>
+      <c r="Z3" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="AA3" s="17" t="s">
+      <c r="AA3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="AB3" s="16"/>
-      <c r="AC3" s="31"/>
+      <c r="AB3" s="14"/>
+      <c r="AC3" s="26"/>
     </row>
     <row r="4" customHeight="1" spans="1:29">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="K4" s="18" t="s">
+      <c r="K4" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="L4" s="18" t="s">
+      <c r="L4" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="M4" s="18" t="s">
+      <c r="M4" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="N4" s="18" t="s">
+      <c r="N4" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="O4" s="18" t="s">
+      <c r="O4" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="P4" s="18" t="s">
+      <c r="P4" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="Q4" s="18" t="s">
+      <c r="Q4" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="18" t="s">
+      <c r="R4" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="18" t="s">
+      <c r="S4" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="T4" s="18" t="s">
+      <c r="T4" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="U4" s="18" t="s">
+      <c r="U4" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="V4" s="18" t="s">
+      <c r="V4" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="W4" s="18" t="s">
+      <c r="W4" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="X4" s="18" t="s">
+      <c r="X4" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="Y4" s="18" t="s">
+      <c r="Y4" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="Z4" s="18" t="s">
+      <c r="Z4" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="AA4" s="18" t="s">
+      <c r="AA4" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="AB4" s="18" t="s">
+      <c r="AB4" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="AC4" s="18" t="s">
+      <c r="AC4" s="27" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1937,8 +1920,8 @@
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
       <c r="I1" s="7"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
       <c r="L1" s="6"/>
       <c r="M1" s="7"/>
       <c r="N1" s="6"/>
@@ -1973,211 +1956,211 @@
       <c r="F2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="13"/>
-      <c r="H2" s="14" t="s">
+      <c r="G2" s="11"/>
+      <c r="H2" s="12" t="s">
         <v>5</v>
       </c>
       <c r="I2" s="11"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="22" t="s">
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="23" t="s">
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="23"/>
-      <c r="U2" s="27" t="s">
+      <c r="T2" s="10"/>
+      <c r="U2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="V2" s="27" t="s">
+      <c r="V2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="W2" s="27"/>
+      <c r="W2" s="23"/>
       <c r="X2" s="10" t="s">
         <v>10</v>
       </c>
       <c r="Y2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z2" s="22" t="s">
+      <c r="Z2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="AA2" s="26"/>
-      <c r="AB2" s="27" t="s">
+      <c r="AA2" s="10"/>
+      <c r="AB2" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="AC2" s="30" t="s">
+      <c r="AC2" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="39.95" customHeight="1" spans="1:29">
-      <c r="A3" s="15"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="17" t="s">
+      <c r="A3" s="13"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="24" t="s">
+      <c r="J3" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="25" t="s">
+      <c r="K3" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="25" t="s">
+      <c r="L3" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="17" t="s">
+      <c r="M3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="25" t="s">
+      <c r="N3" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="17" t="s">
+      <c r="O3" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="P3" s="17" t="s">
+      <c r="P3" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="Q3" s="17" t="s">
+      <c r="Q3" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="R3" s="17" t="s">
+      <c r="R3" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="17" t="s">
+      <c r="S3" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="T3" s="28" t="s">
+      <c r="T3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="16"/>
-      <c r="V3" s="25" t="s">
+      <c r="U3" s="14"/>
+      <c r="V3" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="W3" s="17" t="s">
+      <c r="W3" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="X3" s="29"/>
-      <c r="Y3" s="29"/>
-      <c r="Z3" s="17" t="s">
+      <c r="X3" s="24"/>
+      <c r="Y3" s="24"/>
+      <c r="Z3" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="AA3" s="17" t="s">
+      <c r="AA3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="AB3" s="16"/>
-      <c r="AC3" s="31"/>
+      <c r="AB3" s="14"/>
+      <c r="AC3" s="26"/>
     </row>
     <row r="4" customHeight="1" spans="1:29">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="K4" s="18" t="s">
+      <c r="K4" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="L4" s="18" t="s">
+      <c r="L4" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="M4" s="18" t="s">
+      <c r="M4" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="N4" s="18" t="s">
+      <c r="N4" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="O4" s="18" t="s">
+      <c r="O4" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="P4" s="18" t="s">
+      <c r="P4" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="Q4" s="18" t="s">
+      <c r="Q4" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="18" t="s">
+      <c r="R4" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="18" t="s">
+      <c r="S4" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="T4" s="18" t="s">
+      <c r="T4" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="U4" s="18" t="s">
+      <c r="U4" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="V4" s="18" t="s">
+      <c r="V4" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="W4" s="18" t="s">
+      <c r="W4" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="X4" s="18" t="s">
+      <c r="X4" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="Y4" s="18" t="s">
+      <c r="Y4" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="Z4" s="18" t="s">
+      <c r="Z4" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="AA4" s="18" t="s">
+      <c r="AA4" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="AB4" s="18" t="s">
+      <c r="AB4" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="AC4" s="18" t="s">
+      <c r="AC4" s="27" t="s">
         <v>64</v>
       </c>
     </row>
